--- a/Takeda_Events_2026_Enterprise.xlsx
+++ b/Takeda_Events_2026_Enterprise.xlsx
@@ -17,6 +17,8 @@
     <sheet name="Palestrantes e KOLs" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Mapeamento de Campos" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Log de Migração" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Invoices Staging" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Flow Log" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,11 +27,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="DD/MM/AAAA"/>
-    <numFmt numFmtId="167" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="DD/MM/AAAA"/>
+    <numFmt numFmtId="166" formatCode=""/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -193,7 +194,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -359,11 +360,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="medium">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="medium">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D22128"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D22128"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D22128"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D22128"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -467,16 +548,16 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -565,6 +646,26 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -844,6 +945,37 @@
     <tableColumn id="15" name="Mini Bio"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tbl_Invoices_Staging" displayName="tbl_Invoices_Staging" ref="A1:H2" headerRowCount="1">
+  <autoFilter ref="A1:H2"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="RawEmailSubject"/>
+    <tableColumn id="2" name="FileName"/>
+    <tableColumn id="3" name="EventID"/>
+    <tableColumn id="4" name="Vendor"/>
+    <tableColumn id="5" name="InvoiceId"/>
+    <tableColumn id="6" name="Amount"/>
+    <tableColumn id="7" name="Status"/>
+    <tableColumn id="8" name="ErrorFlag"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl_Flow_Log" displayName="tbl_Flow_Log" ref="A1:E2" headerRowCount="1">
+  <autoFilter ref="A1:E2"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Timestamp"/>
+    <tableColumn id="2" name="EventID"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="ErrorMessage"/>
+    <tableColumn id="5" name="FileName"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1183,59 +1315,73 @@
           <t>TOTAL DE EVENTOS</t>
         </is>
       </c>
+      <c r="B5" s="72" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>EM ANDAMENTO</t>
         </is>
       </c>
+      <c r="D5" s="72" t="n"/>
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>CONCLUÍDOS</t>
         </is>
       </c>
+      <c r="F5" s="72" t="n"/>
       <c r="G5" s="7" t="inlineStr">
         <is>
           <t>PLANEJADOS</t>
         </is>
       </c>
+      <c r="H5" s="72" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>TOTAL PLANEJADO</t>
         </is>
       </c>
+      <c r="J5" s="72" t="n"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>TOTAL REALIZADO</t>
         </is>
       </c>
+      <c r="L5" s="72" t="n"/>
       <c r="M5" s="5" t="inlineStr">
         <is>
           <t>ECONOMIA / SALDO</t>
         </is>
       </c>
+      <c r="N5" s="72" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="8" t="n">
         <v>17</v>
       </c>
+      <c r="B6" s="73" t="n"/>
       <c r="C6" s="8" t="n">
         <v>7</v>
       </c>
+      <c r="D6" s="73" t="n"/>
       <c r="E6" s="8" t="n">
         <v>8</v>
       </c>
+      <c r="F6" s="73" t="n"/>
       <c r="G6" s="8" t="n">
         <v>2</v>
       </c>
+      <c r="H6" s="73" t="n"/>
       <c r="I6" s="9" t="n">
         <v>9918070.620000001</v>
       </c>
+      <c r="J6" s="73" t="n"/>
       <c r="K6" s="9" t="n">
         <v>8546720.33925</v>
       </c>
+      <c r="L6" s="73" t="n"/>
       <c r="M6" s="9" t="n">
         <v>1371350.28075</v>
       </c>
+      <c r="N6" s="73" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1243,59 +1389,73 @@
           <t>NO ORÇAMENTO</t>
         </is>
       </c>
+      <c r="B7" s="72" t="n"/>
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t>ACIMA DO ORÇAMENTO</t>
         </is>
       </c>
+      <c r="D7" s="72" t="n"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>VARIÂNCIA %</t>
         </is>
       </c>
+      <c r="F7" s="72" t="n"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>TOTAL FY25 (R$)</t>
         </is>
       </c>
+      <c r="H7" s="72" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>TOTAL FY26 (R$)</t>
         </is>
       </c>
+      <c r="J7" s="72" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
           <t>TOTAL PAGO (R$)</t>
         </is>
       </c>
+      <c r="L7" s="72" t="n"/>
       <c r="M7" s="4" t="inlineStr">
         <is>
           <t>PGTOS. VENCIDOS</t>
         </is>
       </c>
+      <c r="N7" s="72" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="8" t="n">
         <v>15</v>
       </c>
+      <c r="B8" s="73" t="n"/>
       <c r="C8" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="D8" s="73" t="n"/>
       <c r="E8" s="10" t="n">
         <v>-0.138267847980901</v>
       </c>
+      <c r="F8" s="73" t="n"/>
       <c r="G8" s="9" t="n">
         <v>3919463.82425</v>
       </c>
+      <c r="H8" s="73" t="n"/>
       <c r="I8" s="9" t="n">
         <v>4974823.735</v>
       </c>
+      <c r="J8" s="73" t="n"/>
       <c r="K8" s="9" t="n">
         <v>5965075.819250001</v>
       </c>
+      <c r="L8" s="73" t="n"/>
       <c r="M8" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="N8" s="73" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -2542,6 +2702,187 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D22128"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>RawEmailSubject</t>
+        </is>
+      </c>
+      <c r="B1" s="78" t="inlineStr">
+        <is>
+          <t>FileName</t>
+        </is>
+      </c>
+      <c r="C1" s="78" t="inlineStr">
+        <is>
+          <t>EventID</t>
+        </is>
+      </c>
+      <c r="D1" s="78" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="E1" s="78" t="inlineStr">
+        <is>
+          <t>InvoiceId</t>
+        </is>
+      </c>
+      <c r="F1" s="78" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="G1" s="78" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="78" t="inlineStr">
+        <is>
+          <t>ErrorFlag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="79" t="inlineStr">
+        <is>
+          <t>EVT-2026-015 | Fee Speaker SBAD | NF 12345</t>
+        </is>
+      </c>
+      <c r="B2" s="79" t="inlineStr">
+        <is>
+          <t>BL_70979_Fee_TAKEDA_26-188469_SBAD_FOR.pdf</t>
+        </is>
+      </c>
+      <c r="C2" s="79" t="inlineStr">
+        <is>
+          <t>EVT-015</t>
+        </is>
+      </c>
+      <c r="D2" s="79" t="inlineStr">
+        <is>
+          <t>Parceiros Eventos Ltda</t>
+        </is>
+      </c>
+      <c r="E2" s="79" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="F2" s="79" t="n">
+        <v>9800</v>
+      </c>
+      <c r="G2" s="79" t="inlineStr">
+        <is>
+          <t>Pending Validation</t>
+        </is>
+      </c>
+      <c r="H2" s="79" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00888888"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="78" t="inlineStr">
+        <is>
+          <t>EventID</t>
+        </is>
+      </c>
+      <c r="C1" s="78" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="78" t="inlineStr">
+        <is>
+          <t>ErrorMessage</t>
+        </is>
+      </c>
+      <c r="E1" s="78" t="inlineStr">
+        <is>
+          <t>FileName</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="79" t="inlineStr">
+        <is>
+          <t>2026-06-24T23:59:46Z</t>
+        </is>
+      </c>
+      <c r="B2" s="79" t="inlineStr">
+        <is>
+          <t>EVT-015</t>
+        </is>
+      </c>
+      <c r="C2" s="79" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+      <c r="D2" s="79" t="inlineStr"/>
+      <c r="E2" s="79" t="inlineStr">
+        <is>
+          <t>BL_70979_Fee_TAKEDA_26-188469_SBAD_FOR.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2801,13 +3142,13 @@
           <t>MAR</t>
         </is>
       </c>
-      <c r="I2" s="35" t="n">
+      <c r="I2" s="74" t="n">
         <v>46087</v>
       </c>
-      <c r="J2" s="35" t="n">
+      <c r="J2" s="74" t="n">
         <v>46088</v>
       </c>
-      <c r="K2" s="35" t="n">
+      <c r="K2" s="74" t="n">
         <v>46178</v>
       </c>
       <c r="L2" s="14" t="inlineStr">
@@ -2842,18 +3183,18 @@
         </is>
       </c>
       <c r="S2" s="14" t="inlineStr"/>
-      <c r="T2" s="36" t="inlineStr"/>
-      <c r="U2" s="36" t="inlineStr"/>
-      <c r="V2" s="36" t="inlineStr"/>
-      <c r="W2" s="36" t="inlineStr"/>
+      <c r="T2" s="75" t="inlineStr"/>
+      <c r="U2" s="75" t="inlineStr"/>
+      <c r="V2" s="75" t="inlineStr"/>
+      <c r="W2" s="75" t="inlineStr"/>
       <c r="X2" s="27" t="n">
         <v>259</v>
       </c>
-      <c r="Y2" s="36" t="inlineStr"/>
+      <c r="Y2" s="75" t="inlineStr"/>
       <c r="Z2" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="AA2" s="36" t="inlineStr"/>
+      <c r="AA2" s="75" t="inlineStr"/>
       <c r="AB2" s="14" t="inlineStr">
         <is>
           <t>TAKEDA</t>
@@ -2919,13 +3260,13 @@
           <t>MAI</t>
         </is>
       </c>
-      <c r="I3" s="37" t="n">
+      <c r="I3" s="76" t="n">
         <v>46150</v>
       </c>
-      <c r="J3" s="37" t="n">
+      <c r="J3" s="76" t="n">
         <v>46150</v>
       </c>
-      <c r="K3" s="37" t="n">
+      <c r="K3" s="76" t="n">
         <v>46240</v>
       </c>
       <c r="L3" s="23" t="inlineStr">
@@ -2964,18 +3305,18 @@
           <t>EM-035977</t>
         </is>
       </c>
-      <c r="T3" s="38" t="inlineStr"/>
-      <c r="U3" s="38" t="inlineStr"/>
-      <c r="V3" s="38" t="inlineStr"/>
-      <c r="W3" s="38" t="inlineStr"/>
+      <c r="T3" s="77" t="inlineStr"/>
+      <c r="U3" s="77" t="inlineStr"/>
+      <c r="V3" s="77" t="inlineStr"/>
+      <c r="W3" s="77" t="inlineStr"/>
       <c r="X3" s="30" t="n">
         <v>10</v>
       </c>
       <c r="Y3" s="30" t="n">
         <v>500</v>
       </c>
-      <c r="Z3" s="38" t="inlineStr"/>
-      <c r="AA3" s="38" t="inlineStr"/>
+      <c r="Z3" s="77" t="inlineStr"/>
+      <c r="AA3" s="77" t="inlineStr"/>
       <c r="AB3" s="23" t="inlineStr">
         <is>
           <t>SBIM</t>
@@ -3041,13 +3382,13 @@
           <t>MAI</t>
         </is>
       </c>
-      <c r="I4" s="35" t="n">
+      <c r="I4" s="74" t="n">
         <v>46168</v>
       </c>
-      <c r="J4" s="35" t="n">
+      <c r="J4" s="74" t="n">
         <v>46168</v>
       </c>
-      <c r="K4" s="35" t="n">
+      <c r="K4" s="74" t="n">
         <v>46258</v>
       </c>
       <c r="L4" s="14" t="inlineStr">
@@ -3082,18 +3423,18 @@
         </is>
       </c>
       <c r="S4" s="14" t="inlineStr"/>
-      <c r="T4" s="36" t="inlineStr"/>
-      <c r="U4" s="36" t="inlineStr"/>
-      <c r="V4" s="36" t="inlineStr"/>
-      <c r="W4" s="36" t="inlineStr"/>
+      <c r="T4" s="75" t="inlineStr"/>
+      <c r="U4" s="75" t="inlineStr"/>
+      <c r="V4" s="75" t="inlineStr"/>
+      <c r="W4" s="75" t="inlineStr"/>
       <c r="X4" s="27" t="n">
         <v>500</v>
       </c>
-      <c r="Y4" s="36" t="inlineStr"/>
+      <c r="Y4" s="75" t="inlineStr"/>
       <c r="Z4" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="AA4" s="36" t="inlineStr"/>
+      <c r="AA4" s="75" t="inlineStr"/>
       <c r="AB4" s="14" t="inlineStr">
         <is>
           <t>TAKEDA</t>
@@ -3159,13 +3500,13 @@
           <t>MAR</t>
         </is>
       </c>
-      <c r="I5" s="37" t="n">
+      <c r="I5" s="76" t="n">
         <v>46168</v>
       </c>
-      <c r="J5" s="37" t="n">
+      <c r="J5" s="76" t="n">
         <v>46169</v>
       </c>
-      <c r="K5" s="37" t="n">
+      <c r="K5" s="76" t="n">
         <v>46259</v>
       </c>
       <c r="L5" s="23" t="inlineStr">
@@ -3208,16 +3549,16 @@
           <t>EM-035539</t>
         </is>
       </c>
-      <c r="T5" s="38" t="inlineStr"/>
-      <c r="U5" s="38" t="inlineStr"/>
-      <c r="V5" s="38" t="inlineStr"/>
-      <c r="W5" s="38" t="inlineStr"/>
+      <c r="T5" s="77" t="inlineStr"/>
+      <c r="U5" s="77" t="inlineStr"/>
+      <c r="V5" s="77" t="inlineStr"/>
+      <c r="W5" s="77" t="inlineStr"/>
       <c r="X5" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="Y5" s="38" t="inlineStr"/>
-      <c r="Z5" s="38" t="inlineStr"/>
-      <c r="AA5" s="38" t="inlineStr"/>
+      <c r="Y5" s="77" t="inlineStr"/>
+      <c r="Z5" s="77" t="inlineStr"/>
+      <c r="AA5" s="77" t="inlineStr"/>
       <c r="AB5" s="23" t="inlineStr">
         <is>
           <t>MPM</t>
@@ -3279,13 +3620,13 @@
           <t>MAI</t>
         </is>
       </c>
-      <c r="I6" s="35" t="n">
+      <c r="I6" s="74" t="n">
         <v>46170</v>
       </c>
-      <c r="J6" s="35" t="n">
+      <c r="J6" s="74" t="n">
         <v>46170</v>
       </c>
-      <c r="K6" s="35" t="n">
+      <c r="K6" s="74" t="n">
         <v>46260</v>
       </c>
       <c r="L6" s="14" t="inlineStr">
@@ -3320,16 +3661,16 @@
         </is>
       </c>
       <c r="S6" s="14" t="inlineStr"/>
-      <c r="T6" s="36" t="inlineStr"/>
-      <c r="U6" s="36" t="inlineStr"/>
-      <c r="V6" s="36" t="inlineStr"/>
-      <c r="W6" s="36" t="inlineStr"/>
+      <c r="T6" s="75" t="inlineStr"/>
+      <c r="U6" s="75" t="inlineStr"/>
+      <c r="V6" s="75" t="inlineStr"/>
+      <c r="W6" s="75" t="inlineStr"/>
       <c r="X6" s="27" t="n">
         <v>500</v>
       </c>
-      <c r="Y6" s="36" t="inlineStr"/>
-      <c r="Z6" s="36" t="inlineStr"/>
-      <c r="AA6" s="36" t="inlineStr"/>
+      <c r="Y6" s="75" t="inlineStr"/>
+      <c r="Z6" s="75" t="inlineStr"/>
+      <c r="AA6" s="75" t="inlineStr"/>
       <c r="AB6" s="14" t="inlineStr">
         <is>
           <t>TAKEDA</t>
@@ -3395,13 +3736,13 @@
           <t>MAI</t>
         </is>
       </c>
-      <c r="I7" s="37" t="n">
+      <c r="I7" s="76" t="n">
         <v>46174</v>
       </c>
-      <c r="J7" s="37" t="n">
+      <c r="J7" s="76" t="n">
         <v>46178</v>
       </c>
-      <c r="K7" s="37" t="n">
+      <c r="K7" s="76" t="n">
         <v>46268</v>
       </c>
       <c r="L7" s="23" t="inlineStr">
@@ -3432,18 +3773,18 @@
       <c r="Q7" s="23" t="inlineStr"/>
       <c r="R7" s="23" t="inlineStr"/>
       <c r="S7" s="23" t="inlineStr"/>
-      <c r="T7" s="38" t="inlineStr"/>
-      <c r="U7" s="38" t="inlineStr"/>
-      <c r="V7" s="38" t="inlineStr"/>
-      <c r="W7" s="38" t="inlineStr"/>
+      <c r="T7" s="77" t="inlineStr"/>
+      <c r="U7" s="77" t="inlineStr"/>
+      <c r="V7" s="77" t="inlineStr"/>
+      <c r="W7" s="77" t="inlineStr"/>
       <c r="X7" s="30" t="n">
         <v>4</v>
       </c>
       <c r="Y7" s="30" t="n">
         <v>3500</v>
       </c>
-      <c r="Z7" s="38" t="inlineStr"/>
-      <c r="AA7" s="38" t="inlineStr"/>
+      <c r="Z7" s="77" t="inlineStr"/>
+      <c r="AA7" s="77" t="inlineStr"/>
       <c r="AB7" s="23" t="inlineStr">
         <is>
           <t>ESPID</t>
@@ -3501,13 +3842,13 @@
           <t>MAI</t>
         </is>
       </c>
-      <c r="I8" s="35" t="n">
+      <c r="I8" s="74" t="n">
         <v>46174</v>
       </c>
-      <c r="J8" s="35" t="n">
+      <c r="J8" s="74" t="n">
         <v>46178</v>
       </c>
-      <c r="K8" s="35" t="n">
+      <c r="K8" s="74" t="n">
         <v>46268</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
@@ -3538,16 +3879,16 @@
       <c r="Q8" s="14" t="inlineStr"/>
       <c r="R8" s="14" t="inlineStr"/>
       <c r="S8" s="14" t="inlineStr"/>
-      <c r="T8" s="36" t="inlineStr"/>
-      <c r="U8" s="36" t="inlineStr"/>
-      <c r="V8" s="36" t="inlineStr"/>
-      <c r="W8" s="36" t="inlineStr"/>
+      <c r="T8" s="75" t="inlineStr"/>
+      <c r="U8" s="75" t="inlineStr"/>
+      <c r="V8" s="75" t="inlineStr"/>
+      <c r="W8" s="75" t="inlineStr"/>
       <c r="X8" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="Y8" s="36" t="inlineStr"/>
-      <c r="Z8" s="36" t="inlineStr"/>
-      <c r="AA8" s="36" t="inlineStr"/>
+      <c r="Y8" s="75" t="inlineStr"/>
+      <c r="Z8" s="75" t="inlineStr"/>
+      <c r="AA8" s="75" t="inlineStr"/>
       <c r="AB8" s="14" t="inlineStr">
         <is>
           <t>TAKEDA</t>
@@ -3605,13 +3946,13 @@
           <t>MAI</t>
         </is>
       </c>
-      <c r="I9" s="37" t="n">
+      <c r="I9" s="76" t="n">
         <v>46174</v>
       </c>
-      <c r="J9" s="37" t="n">
+      <c r="J9" s="76" t="n">
         <v>46178</v>
       </c>
-      <c r="K9" s="37" t="n">
+      <c r="K9" s="76" t="n">
         <v>46268</v>
       </c>
       <c r="L9" s="23" t="inlineStr">
@@ -3642,16 +3983,16 @@
       <c r="Q9" s="23" t="inlineStr"/>
       <c r="R9" s="23" t="inlineStr"/>
       <c r="S9" s="23" t="inlineStr"/>
-      <c r="T9" s="38" t="inlineStr"/>
-      <c r="U9" s="38" t="inlineStr"/>
-      <c r="V9" s="38" t="inlineStr"/>
-      <c r="W9" s="38" t="inlineStr"/>
+      <c r="T9" s="77" t="inlineStr"/>
+      <c r="U9" s="77" t="inlineStr"/>
+      <c r="V9" s="77" t="inlineStr"/>
+      <c r="W9" s="77" t="inlineStr"/>
       <c r="X9" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="Y9" s="38" t="inlineStr"/>
-      <c r="Z9" s="38" t="inlineStr"/>
-      <c r="AA9" s="38" t="inlineStr"/>
+      <c r="Y9" s="77" t="inlineStr"/>
+      <c r="Z9" s="77" t="inlineStr"/>
+      <c r="AA9" s="77" t="inlineStr"/>
       <c r="AB9" s="23" t="inlineStr">
         <is>
           <t>TAKEDA</t>
@@ -3709,13 +4050,13 @@
           <t>JUN</t>
         </is>
       </c>
-      <c r="I10" s="35" t="n">
+      <c r="I10" s="74" t="n">
         <v>46197</v>
       </c>
-      <c r="J10" s="35" t="n">
+      <c r="J10" s="74" t="n">
         <v>46199</v>
       </c>
-      <c r="K10" s="35" t="n">
+      <c r="K10" s="74" t="n">
         <v>46289</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
@@ -3758,10 +4099,10 @@
           <t>EM-036105</t>
         </is>
       </c>
-      <c r="T10" s="36" t="inlineStr"/>
-      <c r="U10" s="36" t="inlineStr"/>
-      <c r="V10" s="36" t="inlineStr"/>
-      <c r="W10" s="36" t="inlineStr"/>
+      <c r="T10" s="75" t="inlineStr"/>
+      <c r="U10" s="75" t="inlineStr"/>
+      <c r="V10" s="75" t="inlineStr"/>
+      <c r="W10" s="75" t="inlineStr"/>
       <c r="X10" s="27" t="n">
         <v>31</v>
       </c>
@@ -3771,7 +4112,7 @@
       <c r="Z10" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="AA10" s="36" t="inlineStr"/>
+      <c r="AA10" s="75" t="inlineStr"/>
       <c r="AB10" s="14" t="inlineStr">
         <is>
           <t>CCM</t>
@@ -3841,13 +4182,13 @@
           <t>JUN</t>
         </is>
       </c>
-      <c r="I11" s="37" t="n">
+      <c r="I11" s="76" t="n">
         <v>46200</v>
       </c>
-      <c r="J11" s="37" t="n">
+      <c r="J11" s="76" t="n">
         <v>46200</v>
       </c>
-      <c r="K11" s="37" t="n">
+      <c r="K11" s="76" t="n">
         <v>46290</v>
       </c>
       <c r="L11" s="23" t="inlineStr">
@@ -3882,14 +4223,14 @@
         </is>
       </c>
       <c r="S11" s="23" t="inlineStr"/>
-      <c r="T11" s="38" t="inlineStr"/>
-      <c r="U11" s="38" t="inlineStr"/>
-      <c r="V11" s="38" t="inlineStr"/>
-      <c r="W11" s="38" t="inlineStr"/>
-      <c r="X11" s="38" t="inlineStr"/>
-      <c r="Y11" s="38" t="inlineStr"/>
-      <c r="Z11" s="38" t="inlineStr"/>
-      <c r="AA11" s="38" t="inlineStr"/>
+      <c r="T11" s="77" t="inlineStr"/>
+      <c r="U11" s="77" t="inlineStr"/>
+      <c r="V11" s="77" t="inlineStr"/>
+      <c r="W11" s="77" t="inlineStr"/>
+      <c r="X11" s="77" t="inlineStr"/>
+      <c r="Y11" s="77" t="inlineStr"/>
+      <c r="Z11" s="77" t="inlineStr"/>
+      <c r="AA11" s="77" t="inlineStr"/>
       <c r="AB11" s="23" t="inlineStr">
         <is>
           <t>SBIM</t>
@@ -3951,13 +4292,13 @@
           <t>MAI</t>
         </is>
       </c>
-      <c r="I12" s="35" t="n">
+      <c r="I12" s="74" t="n">
         <v>46245</v>
       </c>
-      <c r="J12" s="35" t="n">
+      <c r="J12" s="74" t="n">
         <v>46245</v>
       </c>
-      <c r="K12" s="35" t="n">
+      <c r="K12" s="74" t="n">
         <v>46335</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
@@ -3992,16 +4333,16 @@
         </is>
       </c>
       <c r="S12" s="14" t="inlineStr"/>
-      <c r="T12" s="36" t="inlineStr"/>
-      <c r="U12" s="36" t="inlineStr"/>
-      <c r="V12" s="36" t="inlineStr"/>
-      <c r="W12" s="36" t="inlineStr"/>
+      <c r="T12" s="75" t="inlineStr"/>
+      <c r="U12" s="75" t="inlineStr"/>
+      <c r="V12" s="75" t="inlineStr"/>
+      <c r="W12" s="75" t="inlineStr"/>
       <c r="X12" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="Y12" s="36" t="inlineStr"/>
-      <c r="Z12" s="36" t="inlineStr"/>
-      <c r="AA12" s="36" t="inlineStr"/>
+      <c r="Y12" s="75" t="inlineStr"/>
+      <c r="Z12" s="75" t="inlineStr"/>
+      <c r="AA12" s="75" t="inlineStr"/>
       <c r="AB12" s="14" t="inlineStr">
         <is>
           <t>TAKEDA</t>
@@ -4063,13 +4404,13 @@
           <t>AGO</t>
         </is>
       </c>
-      <c r="I13" s="37" t="n">
+      <c r="I13" s="76" t="n">
         <v>46248</v>
       </c>
-      <c r="J13" s="37" t="n">
+      <c r="J13" s="76" t="n">
         <v>46249</v>
       </c>
-      <c r="K13" s="37" t="n">
+      <c r="K13" s="76" t="n">
         <v>46339</v>
       </c>
       <c r="L13" s="23" t="inlineStr">
@@ -4104,10 +4445,10 @@
         </is>
       </c>
       <c r="S13" s="23" t="inlineStr"/>
-      <c r="T13" s="38" t="inlineStr"/>
-      <c r="U13" s="38" t="inlineStr"/>
-      <c r="V13" s="38" t="inlineStr"/>
-      <c r="W13" s="38" t="inlineStr"/>
+      <c r="T13" s="77" t="inlineStr"/>
+      <c r="U13" s="77" t="inlineStr"/>
+      <c r="V13" s="77" t="inlineStr"/>
+      <c r="W13" s="77" t="inlineStr"/>
       <c r="X13" s="30" t="n">
         <v>269</v>
       </c>
@@ -4117,7 +4458,7 @@
       <c r="Z13" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="AA13" s="38" t="inlineStr"/>
+      <c r="AA13" s="77" t="inlineStr"/>
       <c r="AB13" s="23" t="inlineStr">
         <is>
           <t>TAKEDA</t>
@@ -4179,13 +4520,13 @@
           <t>AGO</t>
         </is>
       </c>
-      <c r="I14" s="35" t="n">
+      <c r="I14" s="74" t="n">
         <v>46260</v>
       </c>
-      <c r="J14" s="35" t="n">
+      <c r="J14" s="74" t="n">
         <v>46263</v>
       </c>
-      <c r="K14" s="35" t="n">
+      <c r="K14" s="74" t="n">
         <v>46353</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
@@ -4220,13 +4561,13 @@
       </c>
       <c r="R14" s="14" t="inlineStr"/>
       <c r="S14" s="14" t="inlineStr"/>
-      <c r="T14" s="36" t="inlineStr"/>
-      <c r="U14" s="36" t="inlineStr"/>
-      <c r="V14" s="36" t="inlineStr"/>
-      <c r="W14" s="36" t="inlineStr"/>
-      <c r="X14" s="36" t="inlineStr"/>
-      <c r="Y14" s="36" t="inlineStr"/>
-      <c r="Z14" s="36" t="inlineStr"/>
+      <c r="T14" s="75" t="inlineStr"/>
+      <c r="U14" s="75" t="inlineStr"/>
+      <c r="V14" s="75" t="inlineStr"/>
+      <c r="W14" s="75" t="inlineStr"/>
+      <c r="X14" s="75" t="inlineStr"/>
+      <c r="Y14" s="75" t="inlineStr"/>
+      <c r="Z14" s="75" t="inlineStr"/>
       <c r="AA14" s="27" t="n">
         <v>1</v>
       </c>
@@ -4295,13 +4636,13 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="I15" s="37" t="n">
+      <c r="I15" s="76" t="n">
         <v>46308</v>
       </c>
-      <c r="J15" s="37" t="n">
+      <c r="J15" s="76" t="n">
         <v>46312</v>
       </c>
-      <c r="K15" s="37" t="n">
+      <c r="K15" s="76" t="n">
         <v>46402</v>
       </c>
       <c r="L15" s="23" t="inlineStr">
@@ -4332,17 +4673,17 @@
       <c r="Q15" s="23" t="inlineStr"/>
       <c r="R15" s="23" t="inlineStr"/>
       <c r="S15" s="23" t="inlineStr"/>
-      <c r="T15" s="38" t="inlineStr"/>
-      <c r="U15" s="38" t="inlineStr"/>
-      <c r="V15" s="38" t="inlineStr"/>
-      <c r="W15" s="38" t="inlineStr"/>
+      <c r="T15" s="77" t="inlineStr"/>
+      <c r="U15" s="77" t="inlineStr"/>
+      <c r="V15" s="77" t="inlineStr"/>
+      <c r="W15" s="77" t="inlineStr"/>
       <c r="X15" s="30" t="n">
         <v>10</v>
       </c>
       <c r="Y15" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="Z15" s="38" t="inlineStr"/>
+      <c r="Z15" s="77" t="inlineStr"/>
       <c r="AA15" s="30" t="n">
         <v>1</v>
       </c>
@@ -4407,13 +4748,13 @@
           <t>SET</t>
         </is>
       </c>
-      <c r="I16" s="35" t="n">
+      <c r="I16" s="74" t="n">
         <v>46316</v>
       </c>
-      <c r="J16" s="35" t="n">
+      <c r="J16" s="74" t="n">
         <v>46319</v>
       </c>
-      <c r="K16" s="35" t="n">
+      <c r="K16" s="74" t="n">
         <v>46409</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
@@ -4448,17 +4789,17 @@
       </c>
       <c r="R16" s="14" t="inlineStr"/>
       <c r="S16" s="14" t="inlineStr"/>
-      <c r="T16" s="36" t="inlineStr"/>
-      <c r="U16" s="36" t="inlineStr"/>
-      <c r="V16" s="36" t="inlineStr"/>
-      <c r="W16" s="36" t="inlineStr"/>
+      <c r="T16" s="75" t="inlineStr"/>
+      <c r="U16" s="75" t="inlineStr"/>
+      <c r="V16" s="75" t="inlineStr"/>
+      <c r="W16" s="75" t="inlineStr"/>
       <c r="X16" s="27" t="n">
         <v>25</v>
       </c>
       <c r="Y16" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="Z16" s="36" t="inlineStr"/>
+      <c r="Z16" s="75" t="inlineStr"/>
       <c r="AA16" s="27" t="n">
         <v>20</v>
       </c>
@@ -4529,13 +4870,13 @@
           <t>NOV</t>
         </is>
       </c>
-      <c r="I17" s="37" t="n">
+      <c r="I17" s="76" t="n">
         <v>46344</v>
       </c>
-      <c r="J17" s="37" t="n">
+      <c r="J17" s="76" t="n">
         <v>46348</v>
       </c>
-      <c r="K17" s="37" t="n">
+      <c r="K17" s="76" t="n">
         <v>46438</v>
       </c>
       <c r="L17" s="23" t="inlineStr">
@@ -4562,16 +4903,16 @@
       <c r="Q17" s="23" t="inlineStr"/>
       <c r="R17" s="23" t="inlineStr"/>
       <c r="S17" s="23" t="inlineStr"/>
-      <c r="T17" s="38" t="inlineStr"/>
-      <c r="U17" s="38" t="inlineStr"/>
-      <c r="V17" s="38" t="inlineStr"/>
-      <c r="W17" s="38" t="inlineStr"/>
+      <c r="T17" s="77" t="inlineStr"/>
+      <c r="U17" s="77" t="inlineStr"/>
+      <c r="V17" s="77" t="inlineStr"/>
+      <c r="W17" s="77" t="inlineStr"/>
       <c r="X17" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="Y17" s="38" t="inlineStr"/>
-      <c r="Z17" s="38" t="inlineStr"/>
-      <c r="AA17" s="38" t="inlineStr"/>
+      <c r="Y17" s="77" t="inlineStr"/>
+      <c r="Z17" s="77" t="inlineStr"/>
+      <c r="AA17" s="77" t="inlineStr"/>
       <c r="AB17" s="23" t="inlineStr">
         <is>
           <t>SAMT</t>
@@ -4629,13 +4970,13 @@
           <t>NOV</t>
         </is>
       </c>
-      <c r="I18" s="35" t="n">
+      <c r="I18" s="74" t="n">
         <v>46345</v>
       </c>
-      <c r="J18" s="35" t="n">
+      <c r="J18" s="74" t="n">
         <v>46347</v>
       </c>
-      <c r="K18" s="35" t="n">
+      <c r="K18" s="74" t="n">
         <v>46437</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
@@ -4674,10 +5015,10 @@
           <t>EM-035702</t>
         </is>
       </c>
-      <c r="T18" s="36" t="inlineStr"/>
-      <c r="U18" s="36" t="inlineStr"/>
-      <c r="V18" s="36" t="inlineStr"/>
-      <c r="W18" s="36" t="inlineStr"/>
+      <c r="T18" s="75" t="inlineStr"/>
+      <c r="U18" s="75" t="inlineStr"/>
+      <c r="V18" s="75" t="inlineStr"/>
+      <c r="W18" s="75" t="inlineStr"/>
       <c r="X18" s="27" t="n">
         <v>600</v>
       </c>
@@ -6146,7 +6487,7 @@
           <t>2754</t>
         </is>
       </c>
-      <c r="J2" s="35" t="n">
+      <c r="J2" s="74" t="n">
         <v>45968</v>
       </c>
       <c r="K2" s="15" t="inlineStr">
@@ -6232,7 +6573,7 @@
           <t>2553</t>
         </is>
       </c>
-      <c r="J3" s="37" t="n">
+      <c r="J3" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="K3" s="24" t="inlineStr">
@@ -6318,7 +6659,7 @@
           <t>12094</t>
         </is>
       </c>
-      <c r="J4" s="35" t="n">
+      <c r="J4" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K4" s="15" t="inlineStr">
@@ -6404,7 +6745,7 @@
           <t>Recibo 342</t>
         </is>
       </c>
-      <c r="J5" s="37" t="n">
+      <c r="J5" s="76" t="n">
         <v>46195</v>
       </c>
       <c r="K5" s="24" t="inlineStr">
@@ -6490,7 +6831,7 @@
           <t>1407.9</t>
         </is>
       </c>
-      <c r="J6" s="35" t="n">
+      <c r="J6" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K6" s="15" t="inlineStr">
@@ -6576,7 +6917,7 @@
           <t>11326</t>
         </is>
       </c>
-      <c r="J7" s="37" t="n">
+      <c r="J7" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="K7" s="24" t="inlineStr">
@@ -6662,7 +7003,7 @@
           <t>67695</t>
         </is>
       </c>
-      <c r="J8" s="35" t="n">
+      <c r="J8" s="74" t="n">
         <v>46016</v>
       </c>
       <c r="K8" s="15" t="inlineStr">
@@ -6748,7 +7089,7 @@
           <t>70423</t>
         </is>
       </c>
-      <c r="J9" s="37" t="n">
+      <c r="J9" s="76" t="n">
         <v>46196</v>
       </c>
       <c r="K9" s="24" t="inlineStr">
@@ -6834,7 +7175,7 @@
           <t>70461</t>
         </is>
       </c>
-      <c r="J10" s="35" t="n">
+      <c r="J10" s="74" t="n">
         <v>46196</v>
       </c>
       <c r="K10" s="15" t="inlineStr">
@@ -6920,7 +7261,7 @@
           <t>46285</t>
         </is>
       </c>
-      <c r="J11" s="37" t="n">
+      <c r="J11" s="76" t="n">
         <v>46196</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
@@ -7006,7 +7347,7 @@
           <t>46311</t>
         </is>
       </c>
-      <c r="J12" s="35" t="n">
+      <c r="J12" s="74" t="n">
         <v>46196</v>
       </c>
       <c r="K12" s="15" t="inlineStr">
@@ -7092,7 +7433,7 @@
           <t>987</t>
         </is>
       </c>
-      <c r="J13" s="37" t="n">
+      <c r="J13" s="76" t="n">
         <v>46058</v>
       </c>
       <c r="K13" s="24" t="inlineStr">
@@ -7178,7 +7519,7 @@
           <t>1002</t>
         </is>
       </c>
-      <c r="J14" s="35" t="n">
+      <c r="J14" s="74" t="n">
         <v>46220</v>
       </c>
       <c r="K14" s="15" t="inlineStr">
@@ -7264,7 +7605,7 @@
           <t>1002</t>
         </is>
       </c>
-      <c r="J15" s="37" t="n">
+      <c r="J15" s="76" t="n">
         <v>46220</v>
       </c>
       <c r="K15" s="24" t="inlineStr">
@@ -7350,7 +7691,7 @@
           <t>2121</t>
         </is>
       </c>
-      <c r="J16" s="35" t="n">
+      <c r="J16" s="74" t="n">
         <v>46058</v>
       </c>
       <c r="K16" s="15" t="inlineStr">
@@ -7436,7 +7777,7 @@
           <t>2182</t>
         </is>
       </c>
-      <c r="J17" s="37" t="n">
+      <c r="J17" s="76" t="n">
         <v>46220</v>
       </c>
       <c r="K17" s="24" t="inlineStr">
@@ -7522,7 +7863,7 @@
           <t>2182</t>
         </is>
       </c>
-      <c r="J18" s="35" t="n">
+      <c r="J18" s="74" t="n">
         <v>46220</v>
       </c>
       <c r="K18" s="15" t="inlineStr">
@@ -7608,7 +7949,7 @@
           <t>Recibo</t>
         </is>
       </c>
-      <c r="J19" s="37" t="n">
+      <c r="J19" s="76" t="n">
         <v>46188</v>
       </c>
       <c r="K19" s="24" t="inlineStr">
@@ -7694,7 +8035,7 @@
           <t>Recibo</t>
         </is>
       </c>
-      <c r="J20" s="35" t="n">
+      <c r="J20" s="74" t="n">
         <v>46188</v>
       </c>
       <c r="K20" s="15" t="inlineStr">
@@ -7780,7 +8121,7 @@
           <t>324</t>
         </is>
       </c>
-      <c r="J21" s="37" t="n">
+      <c r="J21" s="76" t="n">
         <v>46150</v>
       </c>
       <c r="K21" s="24" t="inlineStr">
@@ -8026,7 +8367,7 @@
           <t>350</t>
         </is>
       </c>
-      <c r="J24" s="35" t="n">
+      <c r="J24" s="74" t="n">
         <v>46223</v>
       </c>
       <c r="K24" s="15" t="inlineStr">
@@ -8432,7 +8773,7 @@
           <t>69022</t>
         </is>
       </c>
-      <c r="J29" s="37" t="n">
+      <c r="J29" s="76" t="n">
         <v>46065</v>
       </c>
       <c r="K29" s="24" t="inlineStr">
@@ -8678,7 +9019,7 @@
           <t>1028</t>
         </is>
       </c>
-      <c r="J32" s="35" t="n">
+      <c r="J32" s="74" t="n">
         <v>46219</v>
       </c>
       <c r="K32" s="15" t="inlineStr">
@@ -8844,7 +9185,7 @@
           <t>2228</t>
         </is>
       </c>
-      <c r="J34" s="35" t="n">
+      <c r="J34" s="74" t="n">
         <v>46219</v>
       </c>
       <c r="K34" s="15" t="inlineStr">
@@ -9314,7 +9655,7 @@
           <t>71166</t>
         </is>
       </c>
-      <c r="J40" s="35" t="n">
+      <c r="J40" s="74" t="n">
         <v>46171</v>
       </c>
       <c r="K40" s="15" t="inlineStr">
@@ -9400,7 +9741,7 @@
           <t>72109</t>
         </is>
       </c>
-      <c r="J41" s="37" t="n">
+      <c r="J41" s="76" t="n">
         <v>46194</v>
       </c>
       <c r="K41" s="24" t="inlineStr">
@@ -9646,7 +9987,7 @@
           <t>70979</t>
         </is>
       </c>
-      <c r="J44" s="35" t="n">
+      <c r="J44" s="74" t="n">
         <v>46153</v>
       </c>
       <c r="K44" s="15" t="inlineStr">
@@ -9892,7 +10233,7 @@
           <t>313</t>
         </is>
       </c>
-      <c r="J47" s="37" t="n">
+      <c r="J47" s="76" t="n">
         <v>46129</v>
       </c>
       <c r="K47" s="24" t="inlineStr">
@@ -10058,7 +10399,7 @@
           <t>1000</t>
         </is>
       </c>
-      <c r="J49" s="37" t="n">
+      <c r="J49" s="76" t="n">
         <v>46129</v>
       </c>
       <c r="K49" s="24" t="inlineStr">
@@ -10144,7 +10485,7 @@
           <t>2179</t>
         </is>
       </c>
-      <c r="J50" s="35" t="n">
+      <c r="J50" s="74" t="n">
         <v>46129</v>
       </c>
       <c r="K50" s="15" t="inlineStr">
@@ -10994,7 +11335,7 @@
           <t>316</t>
         </is>
       </c>
-      <c r="J61" s="37" t="n">
+      <c r="J61" s="76" t="n">
         <v>46132</v>
       </c>
       <c r="K61" s="24" t="inlineStr">
@@ -11080,7 +11421,7 @@
           <t>288454</t>
         </is>
       </c>
-      <c r="J62" s="35" t="n">
+      <c r="J62" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K62" s="15" t="inlineStr">
@@ -11166,7 +11507,7 @@
           <t>11335</t>
         </is>
       </c>
-      <c r="J63" s="37" t="n">
+      <c r="J63" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="K63" s="24" t="inlineStr">
@@ -11252,7 +11593,7 @@
           <t>318</t>
         </is>
       </c>
-      <c r="J64" s="35" t="n">
+      <c r="J64" s="74" t="n">
         <v>46132</v>
       </c>
       <c r="K64" s="15" t="inlineStr">
@@ -11338,7 +11679,7 @@
           <t>288470</t>
         </is>
       </c>
-      <c r="J65" s="37" t="n">
+      <c r="J65" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="K65" s="24" t="inlineStr">
@@ -11424,7 +11765,7 @@
           <t>11336</t>
         </is>
       </c>
-      <c r="J66" s="35" t="n">
+      <c r="J66" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K66" s="15" t="inlineStr">
@@ -11510,7 +11851,7 @@
           <t>1018</t>
         </is>
       </c>
-      <c r="J67" s="37" t="n">
+      <c r="J67" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="K67" s="24" t="inlineStr">
@@ -11596,7 +11937,7 @@
           <t>2212</t>
         </is>
       </c>
-      <c r="J68" s="35" t="n">
+      <c r="J68" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K68" s="15" t="inlineStr">
@@ -11682,7 +12023,7 @@
           <t>317</t>
         </is>
       </c>
-      <c r="J69" s="37" t="n">
+      <c r="J69" s="76" t="n">
         <v>46132</v>
       </c>
       <c r="K69" s="24" t="inlineStr">
@@ -11768,7 +12109,7 @@
           <t>1426-5</t>
         </is>
       </c>
-      <c r="J70" s="35" t="n">
+      <c r="J70" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K70" s="15" t="inlineStr">
@@ -11854,7 +12195,7 @@
           <t>11337</t>
         </is>
       </c>
-      <c r="J71" s="37" t="n">
+      <c r="J71" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="K71" s="24" t="inlineStr">
@@ -11940,7 +12281,7 @@
           <t>11334</t>
         </is>
       </c>
-      <c r="J72" s="35" t="n">
+      <c r="J72" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K72" s="15" t="inlineStr">
@@ -12026,7 +12367,7 @@
           <t>Recibo</t>
         </is>
       </c>
-      <c r="J73" s="37" t="n">
+      <c r="J73" s="76" t="n">
         <v>46178</v>
       </c>
       <c r="K73" s="24" t="inlineStr">
@@ -12112,7 +12453,7 @@
           <t>334</t>
         </is>
       </c>
-      <c r="J74" s="35" t="n">
+      <c r="J74" s="74" t="n">
         <v>46166</v>
       </c>
       <c r="K74" s="15" t="inlineStr">
@@ -12198,7 +12539,7 @@
           <t>1401</t>
         </is>
       </c>
-      <c r="J75" s="37" t="n">
+      <c r="J75" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="K75" s="24" t="inlineStr">
@@ -12284,7 +12625,7 @@
           <t>11322</t>
         </is>
       </c>
-      <c r="J76" s="35" t="n">
+      <c r="J76" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K76" s="15" t="inlineStr">
@@ -12370,7 +12711,7 @@
           <t>1401</t>
         </is>
       </c>
-      <c r="J77" s="37" t="n">
+      <c r="J77" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="K77" s="24" t="inlineStr">
@@ -12456,7 +12797,7 @@
           <t>11322</t>
         </is>
       </c>
-      <c r="J78" s="35" t="n">
+      <c r="J78" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K78" s="15" t="inlineStr">
@@ -12542,7 +12883,7 @@
           <t>Recibo</t>
         </is>
       </c>
-      <c r="J79" s="37" t="n">
+      <c r="J79" s="76" t="n">
         <v>46039</v>
       </c>
       <c r="K79" s="24" t="inlineStr">
@@ -12628,7 +12969,7 @@
           <t>Recibo</t>
         </is>
       </c>
-      <c r="J80" s="35" t="n">
+      <c r="J80" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K80" s="15" t="inlineStr">
@@ -12714,7 +13055,7 @@
           <t>12093</t>
         </is>
       </c>
-      <c r="J81" s="37" t="n">
+      <c r="J81" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="K81" s="24" t="inlineStr">
@@ -12800,7 +13141,7 @@
           <t>338</t>
         </is>
       </c>
-      <c r="J82" s="35" t="n">
+      <c r="J82" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="K82" s="15" t="inlineStr">
@@ -12886,7 +13227,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="J83" s="37" t="n">
+      <c r="J83" s="76" t="n">
         <v>46241</v>
       </c>
       <c r="K83" s="24" t="inlineStr">
@@ -15259,7 +15600,7 @@
           <t>2754</t>
         </is>
       </c>
-      <c r="G2" s="35" t="n">
+      <c r="G2" s="74" t="n">
         <v>45968</v>
       </c>
       <c r="H2" s="15" t="inlineStr">
@@ -15329,7 +15670,7 @@
           <t>2553</t>
         </is>
       </c>
-      <c r="G3" s="37" t="n">
+      <c r="G3" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="H3" s="24" t="inlineStr">
@@ -15399,7 +15740,7 @@
           <t>12094</t>
         </is>
       </c>
-      <c r="G4" s="35" t="n">
+      <c r="G4" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H4" s="15" t="inlineStr">
@@ -15469,7 +15810,7 @@
           <t>Recibo 342</t>
         </is>
       </c>
-      <c r="G5" s="37" t="n">
+      <c r="G5" s="76" t="n">
         <v>46195</v>
       </c>
       <c r="H5" s="24" t="inlineStr">
@@ -15539,7 +15880,7 @@
           <t>1407.9</t>
         </is>
       </c>
-      <c r="G6" s="35" t="n">
+      <c r="G6" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H6" s="15" t="inlineStr">
@@ -15609,7 +15950,7 @@
           <t>11326</t>
         </is>
       </c>
-      <c r="G7" s="37" t="n">
+      <c r="G7" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -15679,7 +16020,7 @@
           <t>67695</t>
         </is>
       </c>
-      <c r="G8" s="35" t="n">
+      <c r="G8" s="74" t="n">
         <v>46016</v>
       </c>
       <c r="H8" s="15" t="inlineStr">
@@ -15749,7 +16090,7 @@
           <t>70423</t>
         </is>
       </c>
-      <c r="G9" s="37" t="n">
+      <c r="G9" s="76" t="n">
         <v>46196</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -15819,7 +16160,7 @@
           <t>70461</t>
         </is>
       </c>
-      <c r="G10" s="35" t="n">
+      <c r="G10" s="74" t="n">
         <v>46196</v>
       </c>
       <c r="H10" s="15" t="inlineStr">
@@ -15889,7 +16230,7 @@
           <t>46285</t>
         </is>
       </c>
-      <c r="G11" s="37" t="n">
+      <c r="G11" s="76" t="n">
         <v>46196</v>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -15959,7 +16300,7 @@
           <t>46311</t>
         </is>
       </c>
-      <c r="G12" s="35" t="n">
+      <c r="G12" s="74" t="n">
         <v>46196</v>
       </c>
       <c r="H12" s="15" t="inlineStr">
@@ -16029,7 +16370,7 @@
           <t>987</t>
         </is>
       </c>
-      <c r="G13" s="37" t="n">
+      <c r="G13" s="76" t="n">
         <v>46058</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -16099,7 +16440,7 @@
           <t>1002</t>
         </is>
       </c>
-      <c r="G14" s="35" t="n">
+      <c r="G14" s="74" t="n">
         <v>46220</v>
       </c>
       <c r="H14" s="15" t="inlineStr">
@@ -16169,7 +16510,7 @@
           <t>1002</t>
         </is>
       </c>
-      <c r="G15" s="37" t="n">
+      <c r="G15" s="76" t="n">
         <v>46220</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -16239,7 +16580,7 @@
           <t>2121</t>
         </is>
       </c>
-      <c r="G16" s="35" t="n">
+      <c r="G16" s="74" t="n">
         <v>46058</v>
       </c>
       <c r="H16" s="15" t="inlineStr">
@@ -16309,7 +16650,7 @@
           <t>2182</t>
         </is>
       </c>
-      <c r="G17" s="37" t="n">
+      <c r="G17" s="76" t="n">
         <v>46220</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -16379,7 +16720,7 @@
           <t>2182</t>
         </is>
       </c>
-      <c r="G18" s="35" t="n">
+      <c r="G18" s="74" t="n">
         <v>46220</v>
       </c>
       <c r="H18" s="15" t="inlineStr">
@@ -16449,7 +16790,7 @@
           <t>Recibo</t>
         </is>
       </c>
-      <c r="G19" s="37" t="n">
+      <c r="G19" s="76" t="n">
         <v>46188</v>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -16519,7 +16860,7 @@
           <t>Recibo</t>
         </is>
       </c>
-      <c r="G20" s="35" t="n">
+      <c r="G20" s="74" t="n">
         <v>46188</v>
       </c>
       <c r="H20" s="15" t="inlineStr">
@@ -16589,7 +16930,7 @@
           <t>324</t>
         </is>
       </c>
-      <c r="G21" s="37" t="n">
+      <c r="G21" s="76" t="n">
         <v>46150</v>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -16787,7 +17128,7 @@
           <t>350</t>
         </is>
       </c>
-      <c r="G24" s="35" t="n">
+      <c r="G24" s="74" t="n">
         <v>46223</v>
       </c>
       <c r="H24" s="15" t="inlineStr">
@@ -17113,7 +17454,7 @@
           <t>69022</t>
         </is>
       </c>
-      <c r="G29" s="37" t="n">
+      <c r="G29" s="76" t="n">
         <v>46065</v>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -17311,7 +17652,7 @@
           <t>1028</t>
         </is>
       </c>
-      <c r="G32" s="35" t="n">
+      <c r="G32" s="74" t="n">
         <v>46219</v>
       </c>
       <c r="H32" s="15" t="inlineStr">
@@ -17445,7 +17786,7 @@
           <t>2228</t>
         </is>
       </c>
-      <c r="G34" s="35" t="n">
+      <c r="G34" s="74" t="n">
         <v>46219</v>
       </c>
       <c r="H34" s="15" t="inlineStr">
@@ -17819,7 +18160,7 @@
           <t>71166</t>
         </is>
       </c>
-      <c r="G40" s="35" t="n">
+      <c r="G40" s="74" t="n">
         <v>46171</v>
       </c>
       <c r="H40" s="15" t="inlineStr">
@@ -17889,7 +18230,7 @@
           <t>72109</t>
         </is>
       </c>
-      <c r="G41" s="37" t="n">
+      <c r="G41" s="76" t="n">
         <v>46194</v>
       </c>
       <c r="H41" s="24" t="inlineStr">
@@ -18087,7 +18428,7 @@
           <t>70979</t>
         </is>
       </c>
-      <c r="G44" s="35" t="n">
+      <c r="G44" s="74" t="n">
         <v>46153</v>
       </c>
       <c r="H44" s="15" t="inlineStr">
@@ -18285,7 +18626,7 @@
           <t>313</t>
         </is>
       </c>
-      <c r="G47" s="37" t="n">
+      <c r="G47" s="76" t="n">
         <v>46129</v>
       </c>
       <c r="H47" s="24" t="inlineStr">
@@ -18419,7 +18760,7 @@
           <t>1000</t>
         </is>
       </c>
-      <c r="G49" s="37" t="n">
+      <c r="G49" s="76" t="n">
         <v>46129</v>
       </c>
       <c r="H49" s="24" t="inlineStr">
@@ -18489,7 +18830,7 @@
           <t>2179</t>
         </is>
       </c>
-      <c r="G50" s="35" t="n">
+      <c r="G50" s="74" t="n">
         <v>46129</v>
       </c>
       <c r="H50" s="15" t="inlineStr">
@@ -19163,7 +19504,7 @@
           <t>316</t>
         </is>
       </c>
-      <c r="G61" s="37" t="n">
+      <c r="G61" s="76" t="n">
         <v>46132</v>
       </c>
       <c r="H61" s="24" t="inlineStr">
@@ -19233,7 +19574,7 @@
           <t>288454</t>
         </is>
       </c>
-      <c r="G62" s="35" t="n">
+      <c r="G62" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H62" s="15" t="inlineStr">
@@ -19303,7 +19644,7 @@
           <t>11335</t>
         </is>
       </c>
-      <c r="G63" s="37" t="n">
+      <c r="G63" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="H63" s="24" t="inlineStr">
@@ -19373,7 +19714,7 @@
           <t>318</t>
         </is>
       </c>
-      <c r="G64" s="35" t="n">
+      <c r="G64" s="74" t="n">
         <v>46132</v>
       </c>
       <c r="H64" s="15" t="inlineStr">
@@ -19443,7 +19784,7 @@
           <t>288470</t>
         </is>
       </c>
-      <c r="G65" s="37" t="n">
+      <c r="G65" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="H65" s="24" t="inlineStr">
@@ -19513,7 +19854,7 @@
           <t>11336</t>
         </is>
       </c>
-      <c r="G66" s="35" t="n">
+      <c r="G66" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H66" s="15" t="inlineStr">
@@ -19583,7 +19924,7 @@
           <t>1018</t>
         </is>
       </c>
-      <c r="G67" s="37" t="n">
+      <c r="G67" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -19653,7 +19994,7 @@
           <t>2212</t>
         </is>
       </c>
-      <c r="G68" s="35" t="n">
+      <c r="G68" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H68" s="15" t="inlineStr">
@@ -19723,7 +20064,7 @@
           <t>317</t>
         </is>
       </c>
-      <c r="G69" s="37" t="n">
+      <c r="G69" s="76" t="n">
         <v>46132</v>
       </c>
       <c r="H69" s="24" t="inlineStr">
@@ -19793,7 +20134,7 @@
           <t>1426-5</t>
         </is>
       </c>
-      <c r="G70" s="35" t="n">
+      <c r="G70" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H70" s="15" t="inlineStr">
@@ -19863,7 +20204,7 @@
           <t>11337</t>
         </is>
       </c>
-      <c r="G71" s="37" t="n">
+      <c r="G71" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="H71" s="24" t="inlineStr">
@@ -19933,7 +20274,7 @@
           <t>11334</t>
         </is>
       </c>
-      <c r="G72" s="35" t="n">
+      <c r="G72" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H72" s="15" t="inlineStr">
@@ -20003,7 +20344,7 @@
           <t>Recibo</t>
         </is>
       </c>
-      <c r="G73" s="37" t="n">
+      <c r="G73" s="76" t="n">
         <v>46178</v>
       </c>
       <c r="H73" s="24" t="inlineStr">
@@ -20073,7 +20414,7 @@
           <t>334</t>
         </is>
       </c>
-      <c r="G74" s="35" t="n">
+      <c r="G74" s="74" t="n">
         <v>46166</v>
       </c>
       <c r="H74" s="15" t="inlineStr">
@@ -20143,7 +20484,7 @@
           <t>1401</t>
         </is>
       </c>
-      <c r="G75" s="37" t="n">
+      <c r="G75" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="H75" s="24" t="inlineStr">
@@ -20213,7 +20554,7 @@
           <t>11322</t>
         </is>
       </c>
-      <c r="G76" s="35" t="n">
+      <c r="G76" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H76" s="15" t="inlineStr">
@@ -20283,7 +20624,7 @@
           <t>1401</t>
         </is>
       </c>
-      <c r="G77" s="37" t="n">
+      <c r="G77" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="H77" s="24" t="inlineStr">
@@ -20353,7 +20694,7 @@
           <t>11322</t>
         </is>
       </c>
-      <c r="G78" s="35" t="n">
+      <c r="G78" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H78" s="15" t="inlineStr">
@@ -20423,7 +20764,7 @@
           <t>Recibo</t>
         </is>
       </c>
-      <c r="G79" s="37" t="n">
+      <c r="G79" s="76" t="n">
         <v>46039</v>
       </c>
       <c r="H79" s="24" t="inlineStr">
@@ -20493,7 +20834,7 @@
           <t>Recibo</t>
         </is>
       </c>
-      <c r="G80" s="35" t="n">
+      <c r="G80" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H80" s="15" t="inlineStr">
@@ -20563,7 +20904,7 @@
           <t>12093</t>
         </is>
       </c>
-      <c r="G81" s="37" t="n">
+      <c r="G81" s="76" t="n">
         <v>46286</v>
       </c>
       <c r="H81" s="24" t="inlineStr">
@@ -20633,7 +20974,7 @@
           <t>338</t>
         </is>
       </c>
-      <c r="G82" s="35" t="n">
+      <c r="G82" s="74" t="n">
         <v>46286</v>
       </c>
       <c r="H82" s="15" t="inlineStr">
@@ -20703,7 +21044,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="G83" s="37" t="n">
+      <c r="G83" s="76" t="n">
         <v>46241</v>
       </c>
       <c r="H83" s="24" t="inlineStr">
@@ -42927,7 +43268,7 @@
           <t>787.959.584-87</t>
         </is>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="74" t="n">
         <v>26163</v>
       </c>
       <c r="F4" s="14" t="inlineStr">
@@ -43031,7 +43372,7 @@
           <t>561.330.812-87</t>
         </is>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="74" t="n">
         <v>26723</v>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -43090,7 +43431,7 @@
           <t>069.113.657-24</t>
         </is>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="76" t="n">
         <v>27542</v>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -43292,7 +43633,7 @@
           <t>729.993.149-49</t>
         </is>
       </c>
-      <c r="E11" s="37" t="n">
+      <c r="E11" s="76" t="n">
         <v>24970</v>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -43392,7 +43733,7 @@
           <t>029.965.209-20</t>
         </is>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E13" s="76" t="n">
         <v>29158</v>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -43733,7 +44074,7 @@
           <t>124.296.997-70</t>
         </is>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="74" t="n">
         <v>32297</v>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -43792,7 +44133,7 @@
           <t>349.402.318-28</t>
         </is>
       </c>
-      <c r="E21" s="37" t="n">
+      <c r="E21" s="76" t="n">
         <v>31139</v>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -43851,7 +44192,7 @@
           <t>596.478.687-15</t>
         </is>
       </c>
-      <c r="E22" s="35" t="n">
+      <c r="E22" s="74" t="n">
         <v>21500</v>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -44294,7 +44635,7 @@
           <t>371.255.080-49</t>
         </is>
       </c>
-      <c r="E30" s="35" t="n">
+      <c r="E30" s="74" t="n">
         <v>23309</v>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -44353,7 +44694,7 @@
           <t>116.212.847-00</t>
         </is>
       </c>
-      <c r="E31" s="37" t="n">
+      <c r="E31" s="76" t="n">
         <v>31559</v>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -44412,7 +44753,7 @@
           <t>106.001.317-77</t>
         </is>
       </c>
-      <c r="E32" s="35" t="n">
+      <c r="E32" s="74" t="n">
         <v>32436</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -44569,7 +44910,7 @@
           <t>276.098.121-53</t>
         </is>
       </c>
-      <c r="E35" s="37" t="n">
+      <c r="E35" s="76" t="n">
         <v>22609</v>
       </c>
       <c r="F35" s="23" t="inlineStr">
@@ -44632,7 +44973,7 @@
           <t>536.227.829-00</t>
         </is>
       </c>
-      <c r="E36" s="35" t="n">
+      <c r="E36" s="74" t="n">
         <v>22960</v>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -44721,7 +45062,7 @@
           <t>843.097.767-87</t>
         </is>
       </c>
-      <c r="E38" s="35" t="n">
+      <c r="E38" s="74" t="n">
         <v>22984</v>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -44787,7 +45128,7 @@
           <t>260.948.598-04</t>
         </is>
       </c>
-      <c r="E39" s="37" t="n">
+      <c r="E39" s="76" t="n">
         <v>28171</v>
       </c>
       <c r="F39" s="23" t="inlineStr">
@@ -44899,7 +45240,7 @@
           <t>164.154.184-91</t>
         </is>
       </c>
-      <c r="E41" s="37" t="n">
+      <c r="E41" s="76" t="n">
         <v>21761</v>
       </c>
       <c r="F41" s="23" t="inlineStr">
@@ -45031,7 +45372,7 @@
           <t>367.899.718-07</t>
         </is>
       </c>
-      <c r="E43" s="37" t="n">
+      <c r="E43" s="76" t="n">
         <v>32043</v>
       </c>
       <c r="F43" s="23" t="inlineStr">
@@ -45090,7 +45431,7 @@
           <t>172.919.098-72</t>
         </is>
       </c>
-      <c r="E44" s="35" t="n">
+      <c r="E44" s="74" t="n">
         <v>14730</v>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -45159,7 +45500,7 @@
           <t>977.490.876-72</t>
         </is>
       </c>
-      <c r="E45" s="37" t="n">
+      <c r="E45" s="76" t="n">
         <v>27724</v>
       </c>
       <c r="F45" s="23" t="inlineStr">
@@ -45438,7 +45779,7 @@
           <t>031.035.373-44</t>
         </is>
       </c>
-      <c r="E50" s="35" t="n">
+      <c r="E50" s="74" t="n">
         <v>33371</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -45660,7 +46001,7 @@
           <t>137.209.106-87</t>
         </is>
       </c>
-      <c r="E54" s="35" t="n">
+      <c r="E54" s="74" t="n">
         <v>17659</v>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -45725,7 +46066,7 @@
           <t>005.053.457-22</t>
         </is>
       </c>
-      <c r="E55" s="37" t="n">
+      <c r="E55" s="76" t="n">
         <v>26616</v>
       </c>
       <c r="F55" s="23" t="inlineStr">
@@ -46043,7 +46384,7 @@
           <t>457.911.206-72</t>
         </is>
       </c>
-      <c r="E61" s="37" t="n">
+      <c r="E61" s="76" t="n">
         <v>21746</v>
       </c>
       <c r="F61" s="23" t="inlineStr">
@@ -46108,7 +46449,7 @@
           <t>371.077.360-72</t>
         </is>
       </c>
-      <c r="E62" s="35" t="n">
+      <c r="E62" s="74" t="n">
         <v>22924</v>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -46314,7 +46655,7 @@
           <t>789.010.064-72</t>
         </is>
       </c>
-      <c r="E66" s="35" t="n">
+      <c r="E66" s="74" t="n">
         <v>26463</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -46373,7 +46714,7 @@
           <t>131.082.087-21</t>
         </is>
       </c>
-      <c r="E67" s="37" t="n">
+      <c r="E67" s="76" t="n">
         <v>32869</v>
       </c>
       <c r="F67" s="23" t="inlineStr">
@@ -46432,7 +46773,7 @@
           <t>669.719.183-04</t>
         </is>
       </c>
-      <c r="E68" s="35" t="n">
+      <c r="E68" s="74" t="n">
         <v>30424</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -46491,7 +46832,7 @@
           <t>033.298.275-05</t>
         </is>
       </c>
-      <c r="E69" s="37" t="n">
+      <c r="E69" s="76" t="n">
         <v>32012</v>
       </c>
       <c r="F69" s="23" t="inlineStr">
@@ -46554,7 +46895,7 @@
           <t>369.935.868-27</t>
         </is>
       </c>
-      <c r="E70" s="35" t="n">
+      <c r="E70" s="74" t="n">
         <v>32946</v>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -46742,7 +47083,7 @@
           <t>866.598.717-72</t>
         </is>
       </c>
-      <c r="E73" s="37" t="n">
+      <c r="E73" s="76" t="n">
         <v>22656</v>
       </c>
       <c r="F73" s="23" t="inlineStr">
@@ -46805,7 +47146,7 @@
           <t>076.238.438-77</t>
         </is>
       </c>
-      <c r="E74" s="35" t="n">
+      <c r="E74" s="74" t="n">
         <v>24294</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -46909,7 +47250,7 @@
           <t>262.910.328-56</t>
         </is>
       </c>
-      <c r="E76" s="35" t="n">
+      <c r="E76" s="74" t="n">
         <v>28154</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
